--- a/Collections/EURO/Slovakia/#EURO#Slovakia#Commemorative#[2009-present]#UNC.xlsx
+++ b/Collections/EURO/Slovakia/#EURO#Slovakia#Commemorative#[2009-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Slovakia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944D1B52-EBE8-4843-AE6A-D66934FCE3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA08B9F-B8A8-47C9-9FF1-A6A4E21A6D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -80,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="54">
   <si>
     <t>Year</t>
   </si>
@@ -237,6 +240,12 @@
   </si>
   <si>
     <t>Subtype_2#Special_marks_1</t>
+  </si>
+  <si>
+    <t>Trenčín – European Capital of Culture 2026</t>
+  </si>
+  <si>
+    <t>50th Anniversary - Czechoslovak National Football Team’s Victory at the 1976 European Championship</t>
   </si>
 </sst>
 </file>
@@ -515,7 +524,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -602,9 +619,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -873,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="13" customWidth="1"/>
@@ -1456,7 +1473,57 @@
         <v>1</v>
       </c>
       <c r="H23" s="11" t="str">
-        <f t="shared" ref="H23" si="7">IF(OR(AND(G23&gt;1,G23&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H23:H24" si="7">IF(OR(AND(G23&gt;1,G23&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="10">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="10">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11" t="str">
+        <f t="shared" ref="H25" si="8">IF(OR(AND(G25&gt;1,G25&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -1468,11 +1535,28 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G4 G6:G15">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G4 G6:G15">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1484,12 +1568,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
+  <conditionalFormatting sqref="G16:G18">
     <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
+  <conditionalFormatting sqref="G16:G18">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1501,12 +1585,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G18">
+  <conditionalFormatting sqref="G19">
     <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16:G18">
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1518,12 +1602,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
+  <conditionalFormatting sqref="G20">
     <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1535,12 +1619,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
+  <conditionalFormatting sqref="G21:G22 G24">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
+  <conditionalFormatting sqref="G21:G22 G24">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1552,12 +1636,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21:G22">
+  <conditionalFormatting sqref="G23">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G21))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21:G22">
+  <conditionalFormatting sqref="G23">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1569,12 +1653,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
+  <conditionalFormatting sqref="G25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
